--- a/ig/FSH/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/FSH/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-07T14:41:51+00:00</t>
+    <t>2024-07-07T15:42:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/FSH/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/FSH/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-07T15:42:27+00:00</t>
+    <t>2024-07-07T16:39:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
